--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,456 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126187979</v>
+      </c>
+      <c r="B3" t="n">
+        <v>98256</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>468029</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6544551</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126187844</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>468029</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6544632</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt med grönpyrola på en yta av ca 3 kvadratm. Varav flera blomställningar med knopp.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126187940</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57651</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>468033</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6544547</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska tretåhack med rinnande kåda. Svårt att se på bilderna pga dålig upplösning men trädet är märkt med band runt.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126188034</v>
+      </c>
+      <c r="B6" t="n">
+        <v>105363</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>468028</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6544558</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Grönpyrola rikligt på ca 2 kvadratmeter. 4 st med blomställningar.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>126187979</v>
       </c>
       <c r="B3" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126187844</v>
       </c>
       <c r="B4" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>126187940</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>126188034</v>
       </c>
       <c r="B6" t="n">
-        <v>105363</v>
+        <v>105365</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>126187979</v>
       </c>
       <c r="B3" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126187844</v>
       </c>
       <c r="B4" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>126188034</v>
       </c>
       <c r="B6" t="n">
-        <v>105365</v>
+        <v>105367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>126187979</v>
       </c>
       <c r="B3" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126187844</v>
       </c>
       <c r="B4" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>126188034</v>
       </c>
       <c r="B6" t="n">
-        <v>105367</v>
+        <v>105371</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>126187979</v>
       </c>
       <c r="B3" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126187844</v>
       </c>
       <c r="B4" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>126187940</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>126188034</v>
       </c>
       <c r="B6" t="n">
-        <v>105371</v>
+        <v>105384</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>126187979</v>
       </c>
       <c r="B3" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126187844</v>
       </c>
       <c r="B4" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>126188034</v>
       </c>
       <c r="B6" t="n">
-        <v>105384</v>
+        <v>105387</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>126187979</v>
       </c>
       <c r="B3" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>126187844</v>
       </c>
       <c r="B4" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>126187940</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>126188034</v>
       </c>
       <c r="B6" t="n">
-        <v>105387</v>
+        <v>105396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,6 +1238,585 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130087746</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>467918</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6544729</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130087361</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>468021</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6544664</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Färska födohack på klen granlåga</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130087339</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>468012</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6544705</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130087617</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>468036</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6544560</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på tall bredvid bäcken, tidigare känt fynd. Fortsatt ringhackad.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130087330</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>468005</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6544720</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen på död gran.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117026760</v>
+        <v>114757998</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -713,20 +708,20 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västanbäck sv, Nrk</t>
+          <t>nb  v, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468062</v>
+        <v>468030</v>
       </c>
       <c r="R2" t="n">
-        <v>6544659</v>
+        <v>6544569</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,17 +748,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tretåhack på gran i avverkningsanmälan.</t>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,57 +790,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126187979</v>
+        <v>114758098</v>
       </c>
       <c r="B3" t="n">
-        <v>98278</v>
+        <v>57737</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Anderstorp N, Nrk</t>
+          <t>nb ö, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468029</v>
+        <v>468024</v>
       </c>
       <c r="R3" t="n">
-        <v>6544551</v>
+        <v>6544567</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,12 +863,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,7 +887,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126187844</v>
+        <v>114758129</v>
       </c>
       <c r="B4" t="n">
-        <v>105396</v>
+        <v>105881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,29 +933,21 @@
           <t>Sw.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Anderstorp N, Nrk</t>
+          <t>nb  v, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468029</v>
+        <v>468027</v>
       </c>
       <c r="R4" t="n">
-        <v>6544632</v>
+        <v>6544574</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -977,17 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Rikligt med grönpyrola på en yta av ca 3 kvadratm. Varav flera blomställningar med knopp.</t>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,10 +1017,15 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126187940</v>
+        <v>117026760</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57281</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1048,20 +1055,20 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Anderstorp N, Nrk</t>
+          <t>Västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468033</v>
+        <v>468062</v>
       </c>
       <c r="R5" t="n">
-        <v>6544547</v>
+        <v>6544659</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,17 +1095,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska tretåhack med rinnande kåda. Svårt att se på bilderna pga dålig upplösning men trädet är märkt med band runt.</t>
+          <t>Tretåhack på gran i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126188034</v>
+        <v>126187979</v>
       </c>
       <c r="B6" t="n">
-        <v>105396</v>
+        <v>98278</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1136,32 +1143,32 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1172,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468028</v>
+        <v>468029</v>
       </c>
       <c r="R6" t="n">
-        <v>6544558</v>
+        <v>6544551</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,11 +1215,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Grönpyrola rikligt på ca 2 kvadratmeter. 4 st med blomställningar.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130087746</v>
+        <v>126187844</v>
       </c>
       <c r="B7" t="n">
-        <v>58112</v>
+        <v>105396</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,41 +1253,49 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Anderstorp N, Anderstorp N, Nrk</t>
+          <t>Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>467918</v>
+        <v>468029</v>
       </c>
       <c r="R7" t="n">
-        <v>6544729</v>
+        <v>6544632</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1309,22 +1319,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med grönpyrola på en yta av ca 3 kvadratm. Varav flera blomställningar med knopp.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,6 +1338,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1351,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130087361</v>
+        <v>126187940</v>
       </c>
       <c r="B8" t="n">
-        <v>57737</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,16 +1368,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1380,24 +1386,27 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Anderstorp N, Anderstorp N, Nrk</t>
+          <t>Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468021</v>
+        <v>468033</v>
       </c>
       <c r="R8" t="n">
-        <v>6544664</v>
+        <v>6544547</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,27 +1430,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>14:04</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Färska födohack på klen granlåga</t>
+          <t>Färska tretåhack med rinnande kåda. Svårt att se på bilderna pga dålig upplösning men trädet är märkt med band runt.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1468,53 +1467,60 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130087339</v>
+        <v>126188034</v>
       </c>
       <c r="B9" t="n">
-        <v>57737</v>
+        <v>105396</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+          <t>Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468012</v>
+        <v>468028</v>
       </c>
       <c r="R9" t="n">
-        <v>6544705</v>
+        <v>6544558</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1538,27 +1544,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Grönpyrola rikligt på ca 2 kvadratmeter. 4 st med blomställningar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,6 +1563,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1585,27 +1582,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130087617</v>
+        <v>130087746</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>58112</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103015</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1613,10 +1610,9 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1625,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>468036</v>
+        <v>467918</v>
       </c>
       <c r="R10" t="n">
-        <v>6544560</v>
+        <v>6544729</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1660,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,12 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Färska ringhack med savflöde på tall bredvid bäcken, tidigare känt fynd. Fortsatt ringhackad.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1702,7 +1693,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130087330</v>
+        <v>130087361</v>
       </c>
       <c r="B11" t="n">
         <v>57737</v>
@@ -1742,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468005</v>
+        <v>468021</v>
       </c>
       <c r="R11" t="n">
-        <v>6544720</v>
+        <v>6544664</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1777,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1787,12 +1778,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen på död gran.</t>
+          <t>Färska födohack på klen granlåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,6 +1807,474 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130087339</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>468012</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6544705</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130087617</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57740</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>468036</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6544560</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska ringhack med savflöde på tall bredvid bäcken, tidigare känt fynd. Fortsatt ringhackad.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130087330</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>468005</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6544720</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen på död gran.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130087561</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57737</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>468037</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6544556</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska födohack på död gran.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>114758129</v>
       </c>
       <c r="B4" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>114757998</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>114758098</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>114758129</v>
       </c>
       <c r="B4" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1585,7 +1585,7 @@
         <v>130087746</v>
       </c>
       <c r="B10" t="n">
-        <v>58113</v>
+        <v>58198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>130087361</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
         <v>130087339</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
         <v>130087617</v>
       </c>
       <c r="B13" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>130087330</v>
       </c>
       <c r="B14" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>130087561</v>
       </c>
       <c r="B15" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -908,7 +908,7 @@
         <v>114758129</v>
       </c>
       <c r="B4" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,27 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114757998</v>
+        <v>114758098</v>
       </c>
       <c r="B2" t="n">
-        <v>57826</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -714,14 +714,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>nb  v, Skogskärr, Nrk</t>
+          <t>nb ö, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>468030</v>
+        <v>468024</v>
       </c>
       <c r="R2" t="n">
-        <v>6544569</v>
+        <v>6544567</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,14 +790,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114758098</v>
+        <v>130087330</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -819,27 +819,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>nb ö, Skogskärr, Nrk</t>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>468024</v>
+        <v>468005</v>
       </c>
       <c r="R3" t="n">
-        <v>6544567</v>
+        <v>6544720</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -863,22 +860,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska födohack vid basen på död gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,10 +907,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114758129</v>
+        <v>130087339</v>
       </c>
       <c r="B4" t="n">
-        <v>105990</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,41 +918,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>nb  v, Skogskärr, Nrk</t>
+          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>468027</v>
+        <v>468012</v>
       </c>
       <c r="R4" t="n">
-        <v>6544574</v>
+        <v>6544705</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +977,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-02-02</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färska födohack på granlåga</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +1006,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1017,32 +1024,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117026760</v>
+        <v>130087361</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1051,27 +1053,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västanbäck sv, Nrk</t>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>468062</v>
+        <v>468021</v>
       </c>
       <c r="R5" t="n">
-        <v>6544659</v>
+        <v>6544664</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1095,17 +1094,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:04</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Tretåhack på gran i avverkningsanmälan.</t>
+          <t>Färska födohack på klen granlåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,10 +1141,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126187979</v>
+        <v>130087498</v>
       </c>
       <c r="B6" t="n">
-        <v>98278</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1143,49 +1152,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Anderstorp N, Nrk</t>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>468029</v>
+        <v>468072</v>
       </c>
       <c r="R6" t="n">
-        <v>6544551</v>
+        <v>6544519</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,12 +1211,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska födohack på rötad stubbe.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,7 +1240,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126187844</v>
+        <v>130087561</v>
       </c>
       <c r="B7" t="n">
-        <v>105396</v>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1253,49 +1269,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Anderstorp N, Nrk</t>
+          <t>Anderstorp N, Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>468029</v>
+        <v>468037</v>
       </c>
       <c r="R7" t="n">
-        <v>6544632</v>
+        <v>6544556</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1319,17 +1328,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt med grönpyrola på en yta av ca 3 kvadratm. Varav flera blomställningar med knopp.</t>
+          <t>Färska födohack på död gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,7 +1357,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1357,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126187940</v>
+        <v>114757998</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1396,14 +1414,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Anderstorp N, Nrk</t>
+          <t>nb  v, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>468033</v>
+        <v>468030</v>
       </c>
       <c r="R8" t="n">
-        <v>6544547</v>
+        <v>6544569</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1430,17 +1448,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Färska tretåhack med rinnande kåda. Svårt att se på bilderna pga dålig upplösning men trädet är märkt med band runt.</t>
+          <t>2024-02-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,57 +1490,53 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126188034</v>
+        <v>117026760</v>
       </c>
       <c r="B9" t="n">
-        <v>105396</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Anderstorp N, Nrk</t>
+          <t>Västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>468028</v>
+        <v>468062</v>
       </c>
       <c r="R9" t="n">
-        <v>6544558</v>
+        <v>6544659</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,17 +1563,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-24</t>
+          <t>2024-04-15</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Grönpyrola rikligt på ca 2 kvadratmeter. 4 st med blomställningar.</t>
+          <t>Tretåhack på gran i avverkningsanmälan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1563,7 +1582,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1582,27 +1600,27 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130087746</v>
+        <v>126187940</v>
       </c>
       <c r="B10" t="n">
-        <v>58198</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103015</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1610,24 +1628,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Anderstorp N, Anderstorp N, Nrk</t>
+          <t>Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>467918</v>
+        <v>468033</v>
       </c>
       <c r="R10" t="n">
-        <v>6544729</v>
+        <v>6544547</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1651,22 +1673,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>14:36</t>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Färska tretåhack med rinnande kåda. Svårt att se på bilderna pga dålig upplösning men trädet är märkt med band runt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130087361</v>
+        <v>130087617</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1704,16 +1721,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1733,10 +1750,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>468021</v>
+        <v>468036</v>
       </c>
       <c r="R11" t="n">
-        <v>6544664</v>
+        <v>6544560</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1768,7 +1785,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1778,12 +1795,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:04</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Färska födohack på klen granlåga</t>
+          <t>Färska ringhack med savflöde på tall bredvid bäcken, tidigare känt fynd. Fortsatt ringhackad.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,53 +1827,60 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130087339</v>
+        <v>126188101</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+          <t>Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>468012</v>
+        <v>467936</v>
       </c>
       <c r="R12" t="n">
-        <v>6544705</v>
+        <v>6544589</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1880,27 +1904,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>14:02</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Färska födohack på granlåga</t>
+          <t>Fjäder fr tjäderhöna. Fint skick på fjädern så såg "färsk" ut.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,35 +1941,39 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130087617</v>
+        <v>130975541</v>
       </c>
       <c r="B13" t="n">
-        <v>57826</v>
+        <v>57141</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>färska spår</t>
@@ -1967,10 +1985,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>468036</v>
+        <v>467892</v>
       </c>
       <c r="R13" t="n">
-        <v>6544560</v>
+        <v>6544730</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1997,27 +2015,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Färska ringhack med savflöde på tall bredvid bäcken, tidigare känt fynd. Fortsatt ringhackad.</t>
+          <t>Färska spårlöpor sen igår av tjäder.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,50 +2062,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130087330</v>
+        <v>130696933</v>
       </c>
       <c r="B14" t="n">
-        <v>57823</v>
+        <v>4775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Anderstorp N, Anderstorp N, Nrk</t>
+          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>468005</v>
+        <v>467998</v>
       </c>
       <c r="R14" t="n">
-        <v>6544720</v>
+        <v>6544737</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2114,27 +2132,27 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Färska födohack vid basen på död gran.</t>
+          <t>På högstubbe.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2161,38 +2179,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130087561</v>
+        <v>130975579</v>
       </c>
       <c r="B15" t="n">
-        <v>57823</v>
+        <v>57947</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102977</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2201,10 +2223,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>468037</v>
+        <v>467892</v>
       </c>
       <c r="R15" t="n">
-        <v>6544556</v>
+        <v>6544730</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2231,27 +2253,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Färska födohack på död gran.</t>
+          <t>Flög fr skogen i syd nordlig riktning och satte sig I ett träd på hygget.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130975579</v>
+        <v>130087746</v>
       </c>
       <c r="B16" t="n">
-        <v>57878</v>
+        <v>58327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2289,21 +2311,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102977</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2311,21 +2333,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Anderstorp N, Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>467892</v>
+        <v>467918</v>
       </c>
       <c r="R16" t="n">
-        <v>6544730</v>
+        <v>6544729</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2352,27 +2369,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flög fr skogen i syd nordlig riktning och satte sig I ett träd på hygget.</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2399,10 +2411,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130975541</v>
+        <v>126187979</v>
       </c>
       <c r="B17" t="n">
-        <v>57073</v>
+        <v>99035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,21 +2422,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2432,24 +2444,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Anderstorp N, Anderstorp N, Nrk</t>
+          <t>Anderstorp N, Nrk</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>467892</v>
+        <v>468029</v>
       </c>
       <c r="R17" t="n">
-        <v>6544730</v>
+        <v>6544551</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2473,27 +2488,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:41</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-01-31</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska spårlöpor sen igår av tjäder.</t>
+          <t>2025-06-24</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2502,6 +2502,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2520,10 +2521,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130696933</v>
+        <v>114758129</v>
       </c>
       <c r="B18" t="n">
-        <v>4773</v>
+        <v>106243</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2531,42 +2532,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100299</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västanbäck sv, Västanbäck sv, Nrk</t>
+          <t>nb  v, Skogskärr, Nrk</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>467998</v>
+        <v>468027</v>
       </c>
       <c r="R18" t="n">
-        <v>6544737</v>
+        <v>6544574</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2590,27 +2590,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2024-02-02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:21</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På högstubbe.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2619,6 +2614,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2634,6 +2630,236 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126187844</v>
+      </c>
+      <c r="B19" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>468029</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6544632</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt med grönpyrola på en yta av ca 3 kvadratm. Varav flera blomställningar med knopp.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126188034</v>
+      </c>
+      <c r="B20" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Anderstorp N, Nrk</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>468028</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6544558</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Nysund</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Grönpyrola rikligt på ca 2 kvadratmeter. 4 st med blomställningar.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41519-2023 artfynd.xlsx
+++ b/artfynd/A 41519-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114758098</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087330</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087339</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1138,6 +1158,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087361</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1255,6 +1280,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087498</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1372,6 +1402,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087561</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,6 +1522,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114757998</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1597,6 +1637,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117026760</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1707,6 +1752,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126187940</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1824,6 +1874,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087617</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1938,6 +1993,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126188101</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2059,6 +2119,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130975541</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2176,6 +2241,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130696933</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2297,6 +2367,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130975579</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2408,6 +2483,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130087746</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2518,6 +2598,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126187979</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2630,6 +2715,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114758129</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2745,6 +2835,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126187844</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2860,8 +2955,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126188034</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>